--- a/frontend/public/chart-template.xlsx
+++ b/frontend/public/chart-template.xlsx
@@ -3,17 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE332DAB-A0E4-4ADB-8AB7-22E8A2234376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78F34402-EE7F-4BD0-8765-7007AC6656E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="2" r:id="rId1"/>
     <sheet name="Charts" sheetId="3" r:id="rId2"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId3"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -32,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
   <si>
     <t>total</t>
   </si>
@@ -62,33 +59,6 @@
   </si>
   <si>
     <t>Index</t>
-  </si>
-  <si>
-    <t>s</t>
-  </si>
-  <si>
-    <t>w</t>
-  </si>
-  <si>
-    <t>e</t>
-  </si>
-  <si>
-    <t>as</t>
-  </si>
-  <si>
-    <t>Cellular</t>
-  </si>
-  <si>
-    <t>d</t>
-  </si>
-  <si>
-    <t>asd</t>
-  </si>
-  <si>
-    <t>qwe</t>
-  </si>
-  <si>
-    <t>zxc</t>
   </si>
   <si>
     <t>Tasa de Conversión</t>
@@ -343,18 +313,6 @@
               <c:f>Data!$A$2:$A$13</c:f>
               <c:strCache>
                 <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
@@ -374,18 +332,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -395,21 +341,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -605,9 +536,6 @@
               <c:f>Data!$F$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Cellular</c:v>
-                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
@@ -627,9 +555,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>23</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -647,9 +572,6 @@
               <c:f>Data!$F$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>as</c:v>
-                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
@@ -669,9 +591,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1223</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -939,9 +858,6 @@
               <c:f>Data!$I$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>s</c:v>
-                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
@@ -961,9 +877,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>12</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -981,9 +894,6 @@
               <c:f>Data!$I$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>e</c:v>
-                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
@@ -1003,9 +913,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>32</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1023,9 +930,6 @@
               <c:f>Data!$I$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>w</c:v>
-                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
@@ -1045,9 +949,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>321</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1065,9 +966,6 @@
               <c:f>Data!$I$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>d</c:v>
-                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
@@ -1087,9 +985,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>122</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1107,9 +1002,6 @@
               <c:f>Data!$I$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
@@ -1129,9 +1021,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>355</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1416,21 +1305,13 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>Data!$N$2:$N$4</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>asd</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>qwe</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>zxc</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -1438,15 +1319,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>12</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1481,21 +1353,13 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>Data!$N$2:$N$4</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>asd</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>qwe</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>zxc</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -1503,15 +1367,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>13</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1827,18 +1682,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="56"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1848,18 +1691,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="56"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1926,18 +1757,6 @@
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
                       <c:ptCount val="56"/>
-                      <c:pt idx="0">
-                        <c:v>1</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>2</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>3</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>4</c:v>
-                      </c:pt>
                     </c:numCache>
                   </c:numRef>
                 </c:cat>
@@ -1953,18 +1772,6 @@
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
                       <c:ptCount val="56"/>
-                      <c:pt idx="0">
-                        <c:v>1</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>2</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>3</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>4</c:v>
-                      </c:pt>
                     </c:numCache>
                   </c:numRef>
                 </c:val>
@@ -4537,105 +4344,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Data"/>
-      <sheetName val="Charts"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="A2">
-            <v>3</v>
-          </cell>
-          <cell r="B2">
-            <v>24</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3">
-            <v>4</v>
-          </cell>
-          <cell r="B3">
-            <v>193</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4">
-            <v>5</v>
-          </cell>
-          <cell r="B4">
-            <v>1269</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5">
-            <v>6</v>
-          </cell>
-          <cell r="B5">
-            <v>475</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6">
-            <v>7</v>
-          </cell>
-          <cell r="B6">
-            <v>642</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7">
-            <v>8</v>
-          </cell>
-          <cell r="B7">
-            <v>497</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8">
-            <v>9</v>
-          </cell>
-          <cell r="B8">
-            <v>1</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9">
-            <v>10</v>
-          </cell>
-          <cell r="B9">
-            <v>23</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10">
-            <v>11</v>
-          </cell>
-          <cell r="B10">
-            <v>392</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11">
-            <v>12</v>
-          </cell>
-          <cell r="B11">
-            <v>5</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A1569318-7096-414C-B43F-F406885E6D09}" name="Tabla3" displayName="Tabla3" ref="F1:G3" totalsRowShown="0" headerRowDxfId="4">
   <autoFilter ref="F1:G3" xr:uid="{A1569318-7096-414C-B43F-F406885E6D09}"/>
@@ -5065,136 +4773,6 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2">
-        <v>23</v>
-      </c>
-      <c r="I2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J2">
-        <v>12</v>
-      </c>
-      <c r="N2" t="s">
-        <v>16</v>
-      </c>
-      <c r="O2">
-        <v>12</v>
-      </c>
-      <c r="P2">
-        <v>2</v>
-      </c>
-      <c r="S2">
-        <v>1</v>
-      </c>
-      <c r="T2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3">
-        <v>1223</v>
-      </c>
-      <c r="I3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J3">
-        <v>32</v>
-      </c>
-      <c r="N3" t="s">
-        <v>17</v>
-      </c>
-      <c r="O3">
-        <v>23</v>
-      </c>
-      <c r="P3">
-        <v>3</v>
-      </c>
-      <c r="S3">
-        <v>2</v>
-      </c>
-      <c r="T3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>4</v>
-      </c>
-      <c r="I4" t="s">
-        <v>11</v>
-      </c>
-      <c r="J4">
-        <v>321</v>
-      </c>
-      <c r="N4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O4">
-        <v>12</v>
-      </c>
-      <c r="P4">
-        <v>13</v>
-      </c>
-      <c r="S4">
-        <v>3</v>
-      </c>
-      <c r="T4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="I5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5">
-        <v>122</v>
-      </c>
-      <c r="S5">
-        <v>4</v>
-      </c>
-      <c r="T5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>355</v>
-      </c>
-    </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" s="3"/>
     </row>
@@ -5223,17 +4801,17 @@
   <sheetData>
     <row r="19" spans="15:23" ht="21" x14ac:dyDescent="0.35">
       <c r="O19" s="4" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="P19" s="4"/>
       <c r="Q19" s="4"/>
       <c r="R19" s="4" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="S19" s="4"/>
       <c r="T19" s="4"/>
       <c r="U19" s="4" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="V19" s="4"/>
       <c r="W19" s="4"/>

--- a/frontend/public/chart-template.xlsx
+++ b/frontend/public/chart-template.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78F34402-EE7F-4BD0-8765-7007AC6656E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48FD6986-AA26-4D8A-8F42-91638A5041F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="2" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
     <t>total</t>
   </si>
@@ -65,9 +65,6 @@
   </si>
   <si>
     <t>Duración Promedio</t>
-  </si>
-  <si>
-    <t>Rentabilidad Proyectada</t>
   </si>
 </sst>
 </file>
@@ -4810,9 +4807,7 @@
       </c>
       <c r="S19" s="4"/>
       <c r="T19" s="4"/>
-      <c r="U19" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="U19" s="4"/>
       <c r="V19" s="4"/>
       <c r="W19" s="4"/>
     </row>
@@ -4829,10 +4824,7 @@
       </c>
       <c r="S20" s="4"/>
       <c r="T20" s="4"/>
-      <c r="U20" s="4">
-        <f>Data!B22</f>
-        <v>0</v>
-      </c>
+      <c r="U20" s="4"/>
       <c r="V20" s="4"/>
       <c r="W20" s="4"/>
     </row>
